--- a/SeKAD/public/uploads/Teachers.xlsx
+++ b/SeKAD/public/uploads/Teachers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Year 3\Sem I\AD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37224ED2-B1A4-4189-80C5-A65A2ACFB6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F20488BD-7D55-42FF-B98E-9F598E8DB0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C817AD1D-EE34-4EBD-B8D2-BAB910392F3B}"/>
   </bookViews>
@@ -1391,9 +1391,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="169" formatCode="0##########"/>
-    <numFmt numFmtId="170" formatCode="############"/>
-    <numFmt numFmtId="171" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="0##########"/>
+    <numFmt numFmtId="165" formatCode="############"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -1435,42 +1435,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6655,7 +6645,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/SeKAD/public/uploads/Teachers.xlsx
+++ b/SeKAD/public/uploads/Teachers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Year 3\Sem I\AD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F20488BD-7D55-42FF-B98E-9F598E8DB0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BB72BF-BA1C-47CC-9AA1-0FEE18B1003F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C817AD1D-EE34-4EBD-B8D2-BAB910392F3B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="451">
   <si>
     <t>Adib Bin Khalid</t>
   </si>
@@ -1305,9 +1305,6 @@
     <t>muni11@example.com</t>
   </si>
   <si>
-    <t>01234567890</t>
-  </si>
-  <si>
     <t>01134567890</t>
   </si>
   <si>
@@ -1318,9 +1315,6 @@
   </si>
   <si>
     <t>Munirama A/P Sugirama</t>
-  </si>
-  <si>
-    <t>01334567890</t>
   </si>
   <si>
     <t>Not Applicable</t>
@@ -1390,10 +1384,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0##########"/>
+  <numFmts count="4">
     <numFmt numFmtId="165" formatCode="############"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="170" formatCode="\+\60\1\ ########"/>
+    <numFmt numFmtId="172" formatCode="\+\60\ ##\ ###\ ####"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -1424,7 +1419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1435,13 +1430,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1456,6 +1444,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1796,21 +1794,21 @@
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" style="9" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" style="6" customWidth="1"/>
     <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.88671875" customWidth="1"/>
     <col min="12" max="12" width="24.88671875" customWidth="1"/>
-    <col min="13" max="13" width="14.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.44140625" style="13" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.5546875" style="13" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -1822,10 +1820,10 @@
       <c r="B1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="12" t="s">
         <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1834,13 +1832,13 @@
       <c r="F1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="7" t="s">
         <v>96</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="4" t="s">
         <v>98</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1852,7 +1850,7 @@
       <c r="L1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="12" t="s">
         <v>102</v>
       </c>
       <c r="N1" s="2" t="s">
@@ -1861,7 +1859,7 @@
       <c r="O1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q1" s="2" t="s">
@@ -1870,7 +1868,7 @@
       <c r="R1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="12" t="s">
         <v>108</v>
       </c>
       <c r="T1" s="2" t="s">
@@ -1890,25 +1888,25 @@
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="11">
         <v>127345001</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="11">
         <v>167345001</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="G2" s="11">
+        <v>431</v>
+      </c>
+      <c r="G2" s="8">
         <v>29587</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="5">
         <v>810101060001</v>
       </c>
       <c r="J2" s="3" t="s">
@@ -1920,7 +1918,7 @@
       <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="11">
         <v>176547501</v>
       </c>
       <c r="N2" s="3" t="s">
@@ -1929,7 +1927,7 @@
       <c r="O2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="11">
         <v>176463001</v>
       </c>
       <c r="Q2" s="3" t="s">
@@ -1938,7 +1936,7 @@
       <c r="R2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="11">
         <v>123456001</v>
       </c>
       <c r="T2" s="3" t="s">
@@ -1958,25 +1956,25 @@
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="11">
         <v>127345002</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="11">
         <v>167345002</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="G3" s="11">
+        <v>432</v>
+      </c>
+      <c r="G3" s="8">
         <v>29984</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="5">
         <v>820202060002</v>
       </c>
       <c r="J3" s="3" t="s">
@@ -1988,7 +1986,7 @@
       <c r="L3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="11">
         <v>176547502</v>
       </c>
       <c r="N3" s="3" t="s">
@@ -1997,7 +1995,7 @@
       <c r="O3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="5">
+      <c r="P3" s="11">
         <v>176463002</v>
       </c>
       <c r="Q3" s="3" t="s">
@@ -2006,7 +2004,7 @@
       <c r="R3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="S3" s="5">
+      <c r="S3" s="11">
         <v>123456002</v>
       </c>
       <c r="T3" s="3" t="s">
@@ -2026,25 +2024,25 @@
       <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="11">
         <v>127345003</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="11">
         <v>167345003</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="G4" s="11">
+      <c r="F4" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="G4" s="8">
         <v>30378</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="5">
         <v>830303060003</v>
       </c>
       <c r="J4" s="3" t="s">
@@ -2056,7 +2054,7 @@
       <c r="L4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="11">
         <v>176547503</v>
       </c>
       <c r="N4" s="3" t="s">
@@ -2065,7 +2063,7 @@
       <c r="O4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="11">
         <v>176463003</v>
       </c>
       <c r="Q4" s="3" t="s">
@@ -2074,7 +2072,7 @@
       <c r="R4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="S4" s="5">
+      <c r="S4" s="11">
         <v>123456003</v>
       </c>
       <c r="T4" s="3" t="s">
@@ -2094,25 +2092,25 @@
       <c r="B5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="11">
         <v>127345004</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="11">
         <v>167345004</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="G5" s="11">
+        <v>434</v>
+      </c>
+      <c r="G5" s="8">
         <v>30776</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="5">
         <v>840404060004</v>
       </c>
       <c r="J5" s="3" t="s">
@@ -2124,7 +2122,7 @@
       <c r="L5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="11">
         <v>176547504</v>
       </c>
       <c r="N5" s="3" t="s">
@@ -2133,7 +2131,7 @@
       <c r="O5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="P5" s="5">
+      <c r="P5" s="11">
         <v>176463004</v>
       </c>
       <c r="Q5" s="3" t="s">
@@ -2142,7 +2140,7 @@
       <c r="R5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="S5" s="5">
+      <c r="S5" s="11">
         <v>123456004</v>
       </c>
       <c r="T5" s="3" t="s">
@@ -2162,25 +2160,25 @@
       <c r="B6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="11">
         <v>127345005</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="11">
         <v>167345005</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="G6" s="11">
+      <c r="F6" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="G6" s="8">
         <v>31172</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="5">
         <v>850505060005</v>
       </c>
       <c r="J6" s="3" t="s">
@@ -2192,7 +2190,7 @@
       <c r="L6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="11">
         <v>176547505</v>
       </c>
       <c r="N6" s="3" t="s">
@@ -2201,7 +2199,7 @@
       <c r="O6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="P6" s="5">
+      <c r="P6" s="11">
         <v>176463005</v>
       </c>
       <c r="Q6" s="3" t="s">
@@ -2210,7 +2208,7 @@
       <c r="R6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="S6" s="5">
+      <c r="S6" s="11">
         <v>123456005</v>
       </c>
       <c r="T6" s="3" t="s">
@@ -2230,25 +2228,25 @@
       <c r="B7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="11">
         <v>127345006</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="11">
         <v>167345006</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="G7" s="11">
+        <v>436</v>
+      </c>
+      <c r="G7" s="8">
         <v>31569</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="5">
         <v>860606060006</v>
       </c>
       <c r="J7" s="3" t="s">
@@ -2260,7 +2258,7 @@
       <c r="L7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="11">
         <v>176547506</v>
       </c>
       <c r="N7" s="3" t="s">
@@ -2269,7 +2267,7 @@
       <c r="O7" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P7" s="5">
+      <c r="P7" s="11">
         <v>176463006</v>
       </c>
       <c r="Q7" s="3" t="s">
@@ -2278,7 +2276,7 @@
       <c r="R7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="S7" s="5">
+      <c r="S7" s="11">
         <v>123456006</v>
       </c>
       <c r="T7" s="3" t="s">
@@ -2298,25 +2296,25 @@
       <c r="B8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="11">
         <v>127345007</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="11">
         <v>167345007</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="G8" s="11">
+        <v>437</v>
+      </c>
+      <c r="G8" s="8">
         <v>31965</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="5">
         <v>870707060007</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -2328,7 +2326,7 @@
       <c r="L8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="11">
         <v>176547507</v>
       </c>
       <c r="N8" s="3" t="s">
@@ -2337,7 +2335,7 @@
       <c r="O8" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="P8" s="5">
+      <c r="P8" s="11">
         <v>176463007</v>
       </c>
       <c r="Q8" s="3" t="s">
@@ -2346,7 +2344,7 @@
       <c r="R8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="S8" s="5">
+      <c r="S8" s="11">
         <v>123456007</v>
       </c>
       <c r="T8" s="3" t="s">
@@ -2366,25 +2364,25 @@
       <c r="B9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="11">
         <v>127345008</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="11">
         <v>167345008</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="11" t="s">
         <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="G9" s="11">
+        <v>438</v>
+      </c>
+      <c r="G9" s="8">
         <v>32363</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="5">
         <v>880808060008</v>
       </c>
       <c r="J9" s="3" t="s">
@@ -2396,7 +2394,7 @@
       <c r="L9" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="11">
         <v>176547508</v>
       </c>
       <c r="N9" s="3" t="s">
@@ -2405,7 +2403,7 @@
       <c r="O9" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="P9" s="5">
+      <c r="P9" s="11">
         <v>176463008</v>
       </c>
       <c r="Q9" s="3" t="s">
@@ -2414,7 +2412,7 @@
       <c r="R9" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="S9" s="5">
+      <c r="S9" s="11">
         <v>123456008</v>
       </c>
       <c r="T9" s="3" t="s">
@@ -2434,25 +2432,25 @@
       <c r="B10" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="11">
         <v>127345009</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="11">
         <v>167345009</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="G10" s="11">
+        <v>439</v>
+      </c>
+      <c r="G10" s="8">
         <v>32760</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="5">
         <v>890909060009</v>
       </c>
       <c r="J10" s="3" t="s">
@@ -2464,7 +2462,7 @@
       <c r="L10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="11">
         <v>176547509</v>
       </c>
       <c r="N10" s="3" t="s">
@@ -2473,7 +2471,7 @@
       <c r="O10" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P10" s="5">
+      <c r="P10" s="11">
         <v>176463009</v>
       </c>
       <c r="Q10" s="3" t="s">
@@ -2482,7 +2480,7 @@
       <c r="R10" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="S10" s="5">
+      <c r="S10" s="11">
         <v>123456009</v>
       </c>
       <c r="T10" s="3" t="s">
@@ -2502,25 +2500,25 @@
       <c r="B11" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="11">
         <v>127345010</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="11">
         <v>167345010</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G11" s="11">
+        <v>440</v>
+      </c>
+      <c r="G11" s="8">
         <v>33156</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="5">
         <v>901010060010</v>
       </c>
       <c r="J11" s="3" t="s">
@@ -2532,7 +2530,7 @@
       <c r="L11" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="11">
         <v>176547510</v>
       </c>
       <c r="N11" s="3" t="s">
@@ -2541,7 +2539,7 @@
       <c r="O11" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="P11" s="5">
+      <c r="P11" s="11">
         <v>176463010</v>
       </c>
       <c r="Q11" s="3" t="s">
@@ -2550,7 +2548,7 @@
       <c r="R11" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="S11" s="5">
+      <c r="S11" s="11">
         <v>123456010</v>
       </c>
       <c r="T11" s="3" t="s">
@@ -2570,25 +2568,25 @@
       <c r="B12" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="11">
         <v>127345011</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="11">
         <v>167345011</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="G12" s="11">
+        <v>441</v>
+      </c>
+      <c r="G12" s="8">
         <v>29231</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="5">
         <v>800111060011</v>
       </c>
       <c r="J12" s="3" t="s">
@@ -2600,7 +2598,7 @@
       <c r="L12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12" s="11">
         <v>176547511</v>
       </c>
       <c r="N12" s="3" t="s">
@@ -2609,7 +2607,7 @@
       <c r="O12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="P12" s="5">
+      <c r="P12" s="11">
         <v>176463011</v>
       </c>
       <c r="Q12" s="3" t="s">
@@ -2618,7 +2616,7 @@
       <c r="R12" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="S12" s="5">
+      <c r="S12" s="11">
         <v>123456011</v>
       </c>
       <c r="T12" s="3" t="s">
@@ -2638,25 +2636,25 @@
       <c r="B13" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="11">
         <v>127345012</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="11">
         <v>167345012</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="G13" s="11">
+        <v>442</v>
+      </c>
+      <c r="G13" s="8">
         <v>29629</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="5">
         <v>810212060012</v>
       </c>
       <c r="J13" s="3" t="s">
@@ -2668,7 +2666,7 @@
       <c r="L13" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="M13" s="5">
+      <c r="M13" s="11">
         <v>176547512</v>
       </c>
       <c r="N13" s="3" t="s">
@@ -2677,7 +2675,7 @@
       <c r="O13" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="P13" s="5">
+      <c r="P13" s="11">
         <v>176463012</v>
       </c>
       <c r="Q13" s="3" t="s">
@@ -2686,7 +2684,7 @@
       <c r="R13" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="S13" s="5">
+      <c r="S13" s="11">
         <v>123456012</v>
       </c>
       <c r="T13" s="3" t="s">
@@ -2706,25 +2704,25 @@
       <c r="B14" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="11">
         <v>127345013</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="11">
         <v>167345013</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="G14" s="11">
+        <v>443</v>
+      </c>
+      <c r="G14" s="8">
         <v>30023</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="5">
         <v>820313060013</v>
       </c>
       <c r="J14" s="3" t="s">
@@ -2736,7 +2734,7 @@
       <c r="L14" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="M14" s="5">
+      <c r="M14" s="11">
         <v>176547513</v>
       </c>
       <c r="N14" s="3" t="s">
@@ -2745,7 +2743,7 @@
       <c r="O14" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="P14" s="5">
+      <c r="P14" s="11">
         <v>176463013</v>
       </c>
       <c r="Q14" s="3" t="s">
@@ -2754,7 +2752,7 @@
       <c r="R14" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="S14" s="5">
+      <c r="S14" s="11">
         <v>123456013</v>
       </c>
       <c r="T14" s="3" t="s">
@@ -2774,25 +2772,25 @@
       <c r="B15" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="11">
         <v>127345014</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="11">
         <v>167345014</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="G15" s="11">
+        <v>444</v>
+      </c>
+      <c r="G15" s="8">
         <v>30420</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="5">
         <v>830414060014</v>
       </c>
       <c r="J15" s="3" t="s">
@@ -2804,7 +2802,7 @@
       <c r="L15" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="M15" s="5">
+      <c r="M15" s="11">
         <v>176547514</v>
       </c>
       <c r="N15" s="3" t="s">
@@ -2813,7 +2811,7 @@
       <c r="O15" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="P15" s="5">
+      <c r="P15" s="11">
         <v>176463014</v>
       </c>
       <c r="Q15" s="3" t="s">
@@ -2822,7 +2820,7 @@
       <c r="R15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="S15" s="5">
+      <c r="S15" s="11">
         <v>123456014</v>
       </c>
       <c r="T15" s="3" t="s">
@@ -2842,25 +2840,25 @@
       <c r="B16" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="11">
         <v>127345015</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="11">
         <v>167345015</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="G16" s="11">
+        <v>445</v>
+      </c>
+      <c r="G16" s="8">
         <v>30817</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="5">
         <v>840515060015</v>
       </c>
       <c r="J16" s="3" t="s">
@@ -2872,7 +2870,7 @@
       <c r="L16" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M16" s="11">
         <v>176547515</v>
       </c>
       <c r="N16" s="3" t="s">
@@ -2881,7 +2879,7 @@
       <c r="O16" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="P16" s="5">
+      <c r="P16" s="11">
         <v>176463015</v>
       </c>
       <c r="Q16" s="3" t="s">
@@ -2890,7 +2888,7 @@
       <c r="R16" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="S16" s="5">
+      <c r="S16" s="11">
         <v>123456015</v>
       </c>
       <c r="T16" s="3" t="s">
@@ -2910,25 +2908,25 @@
       <c r="B17" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="11">
         <v>127345016</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="11">
         <v>167345016</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G17" s="11">
+        <v>446</v>
+      </c>
+      <c r="G17" s="8">
         <v>31214</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="5">
         <v>850616060016</v>
       </c>
       <c r="J17" s="3" t="s">
@@ -2940,7 +2938,7 @@
       <c r="L17" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="M17" s="5">
+      <c r="M17" s="11">
         <v>176547516</v>
       </c>
       <c r="N17" s="3" t="s">
@@ -2949,7 +2947,7 @@
       <c r="O17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="P17" s="5">
+      <c r="P17" s="11">
         <v>176463016</v>
       </c>
       <c r="Q17" s="3" t="s">
@@ -2958,7 +2956,7 @@
       <c r="R17" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="S17" s="5">
+      <c r="S17" s="11">
         <v>123456016</v>
       </c>
       <c r="T17" s="3" t="s">
@@ -2978,25 +2976,25 @@
       <c r="B18" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="11">
         <v>127345017</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="11">
         <v>167345017</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="G18" s="11">
+        <v>447</v>
+      </c>
+      <c r="G18" s="8">
         <v>31610</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="5">
         <v>860717060017</v>
       </c>
       <c r="J18" s="3" t="s">
@@ -3008,7 +3006,7 @@
       <c r="L18" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M18" s="11">
         <v>176547517</v>
       </c>
       <c r="N18" s="3" t="s">
@@ -3017,7 +3015,7 @@
       <c r="O18" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="P18" s="5">
+      <c r="P18" s="11">
         <v>176463017</v>
       </c>
       <c r="Q18" s="3" t="s">
@@ -3026,7 +3024,7 @@
       <c r="R18" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="S18" s="5">
+      <c r="S18" s="11">
         <v>123456017</v>
       </c>
       <c r="T18" s="3" t="s">
@@ -3046,25 +3044,25 @@
       <c r="B19" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="11">
         <v>127345018</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="11">
         <v>167345018</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="G19" s="11">
+        <v>448</v>
+      </c>
+      <c r="G19" s="8">
         <v>32007</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="5">
         <v>870818060018</v>
       </c>
       <c r="J19" s="3" t="s">
@@ -3076,7 +3074,7 @@
       <c r="L19" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M19" s="11">
         <v>176547518</v>
       </c>
       <c r="N19" s="3" t="s">
@@ -3085,7 +3083,7 @@
       <c r="O19" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="P19" s="5">
+      <c r="P19" s="11">
         <v>176463018</v>
       </c>
       <c r="Q19" s="3" t="s">
@@ -3094,7 +3092,7 @@
       <c r="R19" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="S19" s="5">
+      <c r="S19" s="11">
         <v>123456018</v>
       </c>
       <c r="T19" s="3" t="s">
@@ -3114,25 +3112,25 @@
       <c r="B20" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="11">
         <v>127345019</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="11">
         <v>167345019</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="G20" s="11">
+        <v>449</v>
+      </c>
+      <c r="G20" s="8">
         <v>32405</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="5">
         <v>880919060019</v>
       </c>
       <c r="J20" s="3" t="s">
@@ -3144,7 +3142,7 @@
       <c r="L20" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="M20" s="5">
+      <c r="M20" s="11">
         <v>176547519</v>
       </c>
       <c r="N20" s="3" t="s">
@@ -3153,7 +3151,7 @@
       <c r="O20" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="P20" s="5">
+      <c r="P20" s="11">
         <v>176463019</v>
       </c>
       <c r="Q20" s="3" t="s">
@@ -3162,7 +3160,7 @@
       <c r="R20" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="S20" s="5">
+      <c r="S20" s="11">
         <v>123456019</v>
       </c>
       <c r="T20" s="3" t="s">
@@ -3182,25 +3180,25 @@
       <c r="B21" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="11">
         <v>127345020</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="11">
         <v>167345020</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="G21" s="11">
+        <v>450</v>
+      </c>
+      <c r="G21" s="8">
         <v>32801</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="5">
         <v>890920060020</v>
       </c>
       <c r="J21" s="3" t="s">
@@ -3212,7 +3210,7 @@
       <c r="L21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M21" s="5">
+      <c r="M21" s="11">
         <v>176547520</v>
       </c>
       <c r="N21" s="3" t="s">
@@ -3221,7 +3219,7 @@
       <c r="O21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="P21" s="5">
+      <c r="P21" s="11">
         <v>176463020</v>
       </c>
       <c r="Q21" s="3" t="s">
@@ -3230,7 +3228,7 @@
       <c r="R21" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="S21" s="5">
+      <c r="S21" s="11">
         <v>123456020</v>
       </c>
       <c r="T21" s="3" t="s">
@@ -3250,10 +3248,10 @@
       <c r="B22" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="11">
         <v>127345021</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="11">
         <v>167345021</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -3262,13 +3260,13 @@
       <c r="F22" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="8">
         <v>33198</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="5">
         <v>901121060021</v>
       </c>
       <c r="J22" s="3" t="s">
@@ -3280,7 +3278,7 @@
       <c r="L22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M22" s="5">
+      <c r="M22" s="11">
         <v>176547521</v>
       </c>
       <c r="N22" s="3" t="s">
@@ -3289,7 +3287,7 @@
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="5">
+      <c r="P22" s="11">
         <v>176463021</v>
       </c>
       <c r="Q22" s="3" t="s">
@@ -3298,7 +3296,7 @@
       <c r="R22" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="S22" s="5">
+      <c r="S22" s="11">
         <v>123456021</v>
       </c>
       <c r="T22" s="3" t="s">
@@ -3318,10 +3316,10 @@
       <c r="B23" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="11">
         <v>127345022</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="11">
         <v>167345022</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -3330,13 +3328,13 @@
       <c r="F23" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="8">
         <v>29577</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="5">
         <v>801222060022</v>
       </c>
       <c r="J23" s="3" t="s">
@@ -3348,7 +3346,7 @@
       <c r="L23" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M23" s="5">
+      <c r="M23" s="11">
         <v>176547522</v>
       </c>
       <c r="N23" s="3" t="s">
@@ -3357,7 +3355,7 @@
       <c r="O23" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="P23" s="5">
+      <c r="P23" s="11">
         <v>176463022</v>
       </c>
       <c r="Q23" s="3" t="s">
@@ -3366,7 +3364,7 @@
       <c r="R23" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="S23" s="5">
+      <c r="S23" s="11">
         <v>123456022</v>
       </c>
       <c r="T23" s="3" t="s">
@@ -3386,10 +3384,10 @@
       <c r="B24" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="11">
         <v>127345023</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="11">
         <v>167345023</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -3398,13 +3396,13 @@
       <c r="F24" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="8">
         <v>29609</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="5">
         <v>810123060023</v>
       </c>
       <c r="J24" s="3" t="s">
@@ -3416,7 +3414,7 @@
       <c r="L24" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="M24" s="5">
+      <c r="M24" s="11">
         <v>176547523</v>
       </c>
       <c r="N24" s="3" t="s">
@@ -3425,7 +3423,7 @@
       <c r="O24" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P24" s="5">
+      <c r="P24" s="11">
         <v>176463023</v>
       </c>
       <c r="Q24" s="3" t="s">
@@ -3434,7 +3432,7 @@
       <c r="R24" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="S24" s="5">
+      <c r="S24" s="11">
         <v>123456023</v>
       </c>
       <c r="T24" s="3" t="s">
@@ -3454,10 +3452,10 @@
       <c r="B25" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="11">
         <v>127345024</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="11">
         <v>167345024</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -3466,13 +3464,13 @@
       <c r="F25" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="8">
         <v>30006</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="5">
         <v>820224060024</v>
       </c>
       <c r="J25" s="3" t="s">
@@ -3484,7 +3482,7 @@
       <c r="L25" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="M25" s="5">
+      <c r="M25" s="11">
         <v>176547524</v>
       </c>
       <c r="N25" s="3" t="s">
@@ -3493,7 +3491,7 @@
       <c r="O25" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="P25" s="5">
+      <c r="P25" s="11">
         <v>176463024</v>
       </c>
       <c r="Q25" s="3" t="s">
@@ -3502,7 +3500,7 @@
       <c r="R25" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="S25" s="5">
+      <c r="S25" s="11">
         <v>123456024</v>
       </c>
       <c r="T25" s="3" t="s">
@@ -3522,10 +3520,10 @@
       <c r="B26" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="11">
         <v>127345025</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="11">
         <v>167345025</v>
       </c>
       <c r="E26" s="3" t="s">
@@ -3534,13 +3532,13 @@
       <c r="F26" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="8">
         <v>30400</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="5">
         <v>830325060025</v>
       </c>
       <c r="J26" s="3" t="s">
@@ -3552,7 +3550,7 @@
       <c r="L26" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="M26" s="5">
+      <c r="M26" s="11">
         <v>176547525</v>
       </c>
       <c r="N26" s="3" t="s">
@@ -3561,7 +3559,7 @@
       <c r="O26" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="P26" s="5">
+      <c r="P26" s="11">
         <v>176463025</v>
       </c>
       <c r="Q26" s="3" t="s">
@@ -3570,7 +3568,7 @@
       <c r="R26" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="S26" s="5">
+      <c r="S26" s="11">
         <v>123456025</v>
       </c>
       <c r="T26" s="3" t="s">
@@ -3590,10 +3588,10 @@
       <c r="B27" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="11">
         <v>137547011</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="11">
         <v>197547011</v>
       </c>
       <c r="E27" s="3" t="s">
@@ -3602,13 +3600,13 @@
       <c r="F27" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="8">
         <v>28856</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="5">
         <v>790101060011</v>
       </c>
       <c r="J27" s="3" t="s">
@@ -3620,7 +3618,7 @@
       <c r="L27" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="M27" s="5">
+      <c r="M27" s="11">
         <v>186548011</v>
       </c>
       <c r="N27" s="3" t="s">
@@ -3629,7 +3627,7 @@
       <c r="O27" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="P27" s="5">
+      <c r="P27" s="11">
         <v>186467011</v>
       </c>
       <c r="Q27" s="3" t="s">
@@ -3638,7 +3636,7 @@
       <c r="R27" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="S27" s="5">
+      <c r="S27" s="11">
         <v>136546011</v>
       </c>
       <c r="T27" s="3" t="s">
@@ -3658,10 +3656,10 @@
       <c r="B28" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="11">
         <v>137547012</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="11">
         <v>197547012</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -3670,13 +3668,13 @@
       <c r="F28" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="8">
         <v>29253</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="5">
         <v>800202060012</v>
       </c>
       <c r="J28" s="3" t="s">
@@ -3688,7 +3686,7 @@
       <c r="L28" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="M28" s="5">
+      <c r="M28" s="11">
         <v>186548012</v>
       </c>
       <c r="N28" s="3" t="s">
@@ -3697,7 +3695,7 @@
       <c r="O28" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="P28" s="5">
+      <c r="P28" s="11">
         <v>186467012</v>
       </c>
       <c r="Q28" s="3" t="s">
@@ -3706,7 +3704,7 @@
       <c r="R28" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="S28" s="5">
+      <c r="S28" s="11">
         <v>136546012</v>
       </c>
       <c r="T28" s="3" t="s">
@@ -3726,10 +3724,10 @@
       <c r="B29" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="11">
         <v>137547013</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="11">
         <v>197547013</v>
       </c>
       <c r="E29" s="3" t="s">
@@ -3738,13 +3736,13 @@
       <c r="F29" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="8">
         <v>29648</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="5">
         <v>810303060013</v>
       </c>
       <c r="J29" s="3" t="s">
@@ -3756,7 +3754,7 @@
       <c r="L29" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M29" s="5">
+      <c r="M29" s="11">
         <v>186548013</v>
       </c>
       <c r="N29" s="3" t="s">
@@ -3765,7 +3763,7 @@
       <c r="O29" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="P29" s="5">
+      <c r="P29" s="11">
         <v>186467013</v>
       </c>
       <c r="Q29" s="3" t="s">
@@ -3774,7 +3772,7 @@
       <c r="R29" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="S29" s="5">
+      <c r="S29" s="11">
         <v>136546013</v>
       </c>
       <c r="T29" s="3" t="s">
@@ -3794,10 +3792,10 @@
       <c r="B30" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="11">
         <v>137547014</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="11">
         <v>197547014</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -3806,13 +3804,13 @@
       <c r="F30" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="8">
         <v>30045</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="5">
         <v>820404060014</v>
       </c>
       <c r="J30" s="3" t="s">
@@ -3824,7 +3822,7 @@
       <c r="L30" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="M30" s="5">
+      <c r="M30" s="11">
         <v>186548014</v>
       </c>
       <c r="N30" s="3" t="s">
@@ -3833,7 +3831,7 @@
       <c r="O30" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="P30" s="5">
+      <c r="P30" s="11">
         <v>186467014</v>
       </c>
       <c r="Q30" s="3" t="s">
@@ -3842,7 +3840,7 @@
       <c r="R30" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="S30" s="5">
+      <c r="S30" s="11">
         <v>136546014</v>
       </c>
       <c r="T30" s="3" t="s">
@@ -3862,10 +3860,10 @@
       <c r="B31" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="11">
         <v>137547015</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="11">
         <v>197547015</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -3874,13 +3872,13 @@
       <c r="F31" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="8">
         <v>30441</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I31" s="8">
+      <c r="I31" s="5">
         <v>830505060015</v>
       </c>
       <c r="J31" s="3" t="s">
@@ -3892,7 +3890,7 @@
       <c r="L31" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="M31" s="5">
+      <c r="M31" s="11">
         <v>186548015</v>
       </c>
       <c r="N31" s="3" t="s">
@@ -3901,7 +3899,7 @@
       <c r="O31" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="P31" s="5">
+      <c r="P31" s="11">
         <v>186467015</v>
       </c>
       <c r="Q31" s="3" t="s">
@@ -3910,7 +3908,7 @@
       <c r="R31" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="S31" s="5">
+      <c r="S31" s="11">
         <v>136546015</v>
       </c>
       <c r="T31" s="3" t="s">
@@ -3930,10 +3928,10 @@
       <c r="B32" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="11">
         <v>137547016</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="11">
         <v>197547016</v>
       </c>
       <c r="E32" s="3" t="s">
@@ -3942,13 +3940,13 @@
       <c r="F32" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="8">
         <v>30839</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I32" s="8">
+      <c r="I32" s="5">
         <v>840606060016</v>
       </c>
       <c r="J32" s="3" t="s">
@@ -3960,7 +3958,7 @@
       <c r="L32" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="M32" s="5">
+      <c r="M32" s="11">
         <v>186548016</v>
       </c>
       <c r="N32" s="3" t="s">
@@ -3969,7 +3967,7 @@
       <c r="O32" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="P32" s="5">
+      <c r="P32" s="11">
         <v>186467016</v>
       </c>
       <c r="Q32" s="3" t="s">
@@ -3978,7 +3976,7 @@
       <c r="R32" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="S32" s="5">
+      <c r="S32" s="11">
         <v>136546016</v>
       </c>
       <c r="T32" s="3" t="s">
@@ -3998,10 +3996,10 @@
       <c r="B33" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="11">
         <v>137547017</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="11">
         <v>197547017</v>
       </c>
       <c r="E33" s="3" t="s">
@@ -4010,13 +4008,13 @@
       <c r="F33" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="8">
         <v>31235</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I33" s="8">
+      <c r="I33" s="5">
         <v>850707060017</v>
       </c>
       <c r="J33" s="3" t="s">
@@ -4028,7 +4026,7 @@
       <c r="L33" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="M33" s="5">
+      <c r="M33" s="11">
         <v>186548017</v>
       </c>
       <c r="N33" s="3" t="s">
@@ -4037,7 +4035,7 @@
       <c r="O33" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="P33" s="5">
+      <c r="P33" s="11">
         <v>186467017</v>
       </c>
       <c r="Q33" s="3" t="s">
@@ -4046,7 +4044,7 @@
       <c r="R33" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="S33" s="5">
+      <c r="S33" s="11">
         <v>136546017</v>
       </c>
       <c r="T33" s="3" t="s">
@@ -4066,10 +4064,10 @@
       <c r="B34" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="11">
         <v>137547018</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="11">
         <v>197547018</v>
       </c>
       <c r="E34" s="3" t="s">
@@ -4078,13 +4076,13 @@
       <c r="F34" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G34" s="11">
+      <c r="G34" s="8">
         <v>31632</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I34" s="8">
+      <c r="I34" s="5">
         <v>860808060018</v>
       </c>
       <c r="J34" s="3" t="s">
@@ -4096,7 +4094,7 @@
       <c r="L34" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="M34" s="5">
+      <c r="M34" s="11">
         <v>186548018</v>
       </c>
       <c r="N34" s="3" t="s">
@@ -4105,7 +4103,7 @@
       <c r="O34" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="P34" s="5">
+      <c r="P34" s="11">
         <v>186467018</v>
       </c>
       <c r="Q34" s="3" t="s">
@@ -4114,7 +4112,7 @@
       <c r="R34" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="S34" s="5">
+      <c r="S34" s="11">
         <v>136546018</v>
       </c>
       <c r="T34" s="3" t="s">
@@ -4134,10 +4132,10 @@
       <c r="B35" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="11">
         <v>137547019</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="11">
         <v>197547019</v>
       </c>
       <c r="E35" s="3" t="s">
@@ -4146,13 +4144,13 @@
       <c r="F35" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G35" s="11">
+      <c r="G35" s="8">
         <v>32029</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I35" s="8">
+      <c r="I35" s="5">
         <v>870909060019</v>
       </c>
       <c r="J35" s="3" t="s">
@@ -4164,7 +4162,7 @@
       <c r="L35" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="M35" s="5">
+      <c r="M35" s="11">
         <v>186548019</v>
       </c>
       <c r="N35" s="3" t="s">
@@ -4173,7 +4171,7 @@
       <c r="O35" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="P35" s="5">
+      <c r="P35" s="11">
         <v>186467019</v>
       </c>
       <c r="Q35" s="3" t="s">
@@ -4182,7 +4180,7 @@
       <c r="R35" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="S35" s="5">
+      <c r="S35" s="11">
         <v>136546019</v>
       </c>
       <c r="T35" s="3" t="s">
@@ -4202,10 +4200,10 @@
       <c r="B36" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="11">
         <v>137547020</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="11">
         <v>197547020</v>
       </c>
       <c r="E36" s="3" t="s">
@@ -4214,13 +4212,13 @@
       <c r="F36" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G36" s="11">
+      <c r="G36" s="8">
         <v>32426</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I36" s="8">
+      <c r="I36" s="5">
         <v>881010060020</v>
       </c>
       <c r="J36" s="3" t="s">
@@ -4232,7 +4230,7 @@
       <c r="L36" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="M36" s="5">
+      <c r="M36" s="11">
         <v>186548020</v>
       </c>
       <c r="N36" s="3" t="s">
@@ -4241,7 +4239,7 @@
       <c r="O36" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="P36" s="5">
+      <c r="P36" s="11">
         <v>186467020</v>
       </c>
       <c r="Q36" s="3" t="s">
@@ -4250,7 +4248,7 @@
       <c r="R36" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="S36" s="5">
+      <c r="S36" s="11">
         <v>136546020</v>
       </c>
       <c r="T36" s="3" t="s">
@@ -4270,10 +4268,10 @@
       <c r="B37" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="11">
         <v>137547021</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="11">
         <v>197547021</v>
       </c>
       <c r="E37" s="3" t="s">
@@ -4282,13 +4280,13 @@
       <c r="F37" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G37" s="11">
+      <c r="G37" s="8">
         <v>32823</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I37" s="8">
+      <c r="I37" s="5">
         <v>891111060021</v>
       </c>
       <c r="J37" s="3" t="s">
@@ -4300,7 +4298,7 @@
       <c r="L37" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="M37" s="5">
+      <c r="M37" s="11">
         <v>186548021</v>
       </c>
       <c r="N37" s="3" t="s">
@@ -4309,7 +4307,7 @@
       <c r="O37" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="P37" s="5">
+      <c r="P37" s="11">
         <v>186467021</v>
       </c>
       <c r="Q37" s="3" t="s">
@@ -4318,7 +4316,7 @@
       <c r="R37" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="S37" s="5">
+      <c r="S37" s="11">
         <v>136546021</v>
       </c>
       <c r="T37" s="3" t="s">
@@ -4338,10 +4336,10 @@
       <c r="B38" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38" s="11">
         <v>137547022</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="11">
         <v>197547022</v>
       </c>
       <c r="E38" s="3" t="s">
@@ -4350,13 +4348,13 @@
       <c r="F38" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G38" s="11">
+      <c r="G38" s="8">
         <v>33219</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I38" s="8">
+      <c r="I38" s="5">
         <v>901212060022</v>
       </c>
       <c r="J38" s="3" t="s">
@@ -4368,7 +4366,7 @@
       <c r="L38" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="M38" s="5">
+      <c r="M38" s="11">
         <v>186548022</v>
       </c>
       <c r="N38" s="3" t="s">
@@ -4377,7 +4375,7 @@
       <c r="O38" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="P38" s="5">
+      <c r="P38" s="11">
         <v>186467022</v>
       </c>
       <c r="Q38" s="3" t="s">
@@ -4386,7 +4384,7 @@
       <c r="R38" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="S38" s="5">
+      <c r="S38" s="11">
         <v>136546022</v>
       </c>
       <c r="T38" s="3" t="s">
@@ -4406,10 +4404,10 @@
       <c r="B39" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="11">
         <v>137547023</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="11">
         <v>197547023</v>
       </c>
       <c r="E39" s="3" t="s">
@@ -4418,13 +4416,13 @@
       <c r="F39" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G39" s="11">
+      <c r="G39" s="8">
         <v>33251</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I39" s="8">
+      <c r="I39" s="5">
         <v>910113060023</v>
       </c>
       <c r="J39" s="3" t="s">
@@ -4436,7 +4434,7 @@
       <c r="L39" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="M39" s="5">
+      <c r="M39" s="11">
         <v>186548023</v>
       </c>
       <c r="N39" s="3" t="s">
@@ -4445,7 +4443,7 @@
       <c r="O39" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="P39" s="5">
+      <c r="P39" s="11">
         <v>186467023</v>
       </c>
       <c r="Q39" s="3" t="s">
@@ -4454,7 +4452,7 @@
       <c r="R39" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="S39" s="5">
+      <c r="S39" s="11">
         <v>136546023</v>
       </c>
       <c r="T39" s="3" t="s">
@@ -4474,10 +4472,10 @@
       <c r="B40" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="11">
         <v>137547024</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="11">
         <v>197547024</v>
       </c>
       <c r="E40" s="3" t="s">
@@ -4486,13 +4484,13 @@
       <c r="F40" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G40" s="11">
+      <c r="G40" s="8">
         <v>33648</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I40" s="8">
+      <c r="I40" s="5">
         <v>920214060024</v>
       </c>
       <c r="J40" s="3" t="s">
@@ -4504,7 +4502,7 @@
       <c r="L40" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="M40" s="5">
+      <c r="M40" s="11">
         <v>186548024</v>
       </c>
       <c r="N40" s="3" t="s">
@@ -4513,7 +4511,7 @@
       <c r="O40" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="P40" s="5">
+      <c r="P40" s="11">
         <v>186467024</v>
       </c>
       <c r="Q40" s="3" t="s">
@@ -4522,7 +4520,7 @@
       <c r="R40" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="S40" s="5">
+      <c r="S40" s="11">
         <v>136546024</v>
       </c>
       <c r="T40" s="3" t="s">
@@ -4542,10 +4540,10 @@
       <c r="B41" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C41" s="11">
         <v>137547025</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="11">
         <v>197547025</v>
       </c>
       <c r="E41" s="3" t="s">
@@ -4554,13 +4552,13 @@
       <c r="F41" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G41" s="11">
+      <c r="G41" s="8">
         <v>34043</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I41" s="8">
+      <c r="I41" s="5">
         <v>930315060025</v>
       </c>
       <c r="J41" s="3" t="s">
@@ -4572,7 +4570,7 @@
       <c r="L41" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="M41" s="5">
+      <c r="M41" s="11">
         <v>186548025</v>
       </c>
       <c r="N41" s="3" t="s">
@@ -4581,7 +4579,7 @@
       <c r="O41" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="P41" s="5">
+      <c r="P41" s="11">
         <v>186467025</v>
       </c>
       <c r="Q41" s="3" t="s">
@@ -4590,7 +4588,7 @@
       <c r="R41" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="S41" s="5">
+      <c r="S41" s="11">
         <v>136546025</v>
       </c>
       <c r="T41" s="3" t="s">
@@ -4610,10 +4608,10 @@
       <c r="B42" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="11">
         <v>123456001</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="11">
         <v>173456001</v>
       </c>
       <c r="E42" s="3" t="s">
@@ -4622,13 +4620,13 @@
       <c r="F42" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G42" s="11">
+      <c r="G42" s="8">
         <v>29351</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I42" s="8">
+      <c r="I42" s="5">
         <v>800510100001</v>
       </c>
       <c r="J42" s="3" t="s">
@@ -4640,7 +4638,7 @@
       <c r="L42" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="M42" s="5">
+      <c r="M42" s="11">
         <v>163457001</v>
       </c>
       <c r="N42" s="3" t="s">
@@ -4649,7 +4647,7 @@
       <c r="O42" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="P42" s="5">
+      <c r="P42" s="11">
         <v>173458001</v>
       </c>
       <c r="Q42" s="3" t="s">
@@ -4658,7 +4656,7 @@
       <c r="R42" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S42" s="5">
+      <c r="S42" s="11">
         <v>163457001</v>
       </c>
       <c r="T42" s="3" t="s">
@@ -4678,10 +4676,10 @@
       <c r="B43" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="11">
         <v>123456002</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="11">
         <v>173456002</v>
       </c>
       <c r="E43" s="3" t="s">
@@ -4690,13 +4688,13 @@
       <c r="F43" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G43" s="11">
+      <c r="G43" s="8">
         <v>29810</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I43" s="8">
+      <c r="I43" s="5">
         <v>810812100002</v>
       </c>
       <c r="J43" s="3" t="s">
@@ -4708,7 +4706,7 @@
       <c r="L43" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="M43" s="5">
+      <c r="M43" s="11">
         <v>163457002</v>
       </c>
       <c r="N43" s="3" t="s">
@@ -4717,7 +4715,7 @@
       <c r="O43" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="P43" s="5">
+      <c r="P43" s="11">
         <v>173458002</v>
       </c>
       <c r="Q43" s="3" t="s">
@@ -4726,7 +4724,7 @@
       <c r="R43" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="S43" s="5">
+      <c r="S43" s="11">
         <v>173458002</v>
       </c>
       <c r="T43" s="3" t="s">
@@ -4746,10 +4744,10 @@
       <c r="B44" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="11">
         <v>123456003</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="11">
         <v>173456003</v>
       </c>
       <c r="E44" s="3" t="s">
@@ -4758,13 +4756,13 @@
       <c r="F44" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G44" s="11">
+      <c r="G44" s="8">
         <v>30035</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I44" s="8">
+      <c r="I44" s="5">
         <v>820325100003</v>
       </c>
       <c r="J44" s="3" t="s">
@@ -4776,7 +4774,7 @@
       <c r="L44" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="M44" s="5">
+      <c r="M44" s="11">
         <v>163457003</v>
       </c>
       <c r="N44" s="3" t="s">
@@ -4785,7 +4783,7 @@
       <c r="O44" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="P44" s="5">
+      <c r="P44" s="11">
         <v>173458003</v>
       </c>
       <c r="Q44" s="3" t="s">
@@ -4794,7 +4792,7 @@
       <c r="R44" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S44" s="5">
+      <c r="S44" s="11">
         <v>163457003</v>
       </c>
       <c r="T44" s="3" t="s">
@@ -4814,10 +4812,10 @@
       <c r="B45" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C45" s="11">
         <v>123456004</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="11">
         <v>173456004</v>
       </c>
       <c r="E45" s="3" t="s">
@@ -4826,13 +4824,13 @@
       <c r="F45" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G45" s="11">
+      <c r="G45" s="8">
         <v>30574</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I45" s="8">
+      <c r="I45" s="5">
         <v>830915100004</v>
       </c>
       <c r="J45" s="3" t="s">
@@ -4844,7 +4842,7 @@
       <c r="L45" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="M45" s="5">
+      <c r="M45" s="11">
         <v>163457004</v>
       </c>
       <c r="N45" s="3" t="s">
@@ -4853,7 +4851,7 @@
       <c r="O45" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="P45" s="5">
+      <c r="P45" s="11">
         <v>173458004</v>
       </c>
       <c r="Q45" s="3" t="s">
@@ -4862,7 +4860,7 @@
       <c r="R45" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="S45" s="5">
+      <c r="S45" s="11">
         <v>173458004</v>
       </c>
       <c r="T45" s="3" t="s">
@@ -4882,10 +4880,10 @@
       <c r="B46" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C46" s="5">
+      <c r="C46" s="11">
         <v>123456005</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="11">
         <v>173456005</v>
       </c>
       <c r="E46" s="3" t="s">
@@ -4894,13 +4892,13 @@
       <c r="F46" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G46" s="11">
+      <c r="G46" s="8">
         <v>30993</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I46" s="8">
+      <c r="I46" s="5">
         <v>841107100005</v>
       </c>
       <c r="J46" s="3" t="s">
@@ -4912,7 +4910,7 @@
       <c r="L46" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="M46" s="5">
+      <c r="M46" s="11">
         <v>163457005</v>
       </c>
       <c r="N46" s="3" t="s">
@@ -4921,7 +4919,7 @@
       <c r="O46" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="P46" s="5">
+      <c r="P46" s="11">
         <v>173458005</v>
       </c>
       <c r="Q46" s="3" t="s">
@@ -4930,7 +4928,7 @@
       <c r="R46" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S46" s="5">
+      <c r="S46" s="11">
         <v>163457005</v>
       </c>
       <c r="T46" s="3" t="s">
@@ -4950,10 +4948,10 @@
       <c r="B47" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C47" s="5">
+      <c r="C47" s="11">
         <v>123456006</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="11">
         <v>173456006</v>
       </c>
       <c r="E47" s="3" t="s">
@@ -4962,13 +4960,13 @@
       <c r="F47" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G47" s="8">
         <v>31065</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I47" s="8">
+      <c r="I47" s="5">
         <v>850118100006</v>
       </c>
       <c r="J47" s="3" t="s">
@@ -4980,7 +4978,7 @@
       <c r="L47" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="M47" s="5">
+      <c r="M47" s="11">
         <v>163457006</v>
       </c>
       <c r="N47" s="3" t="s">
@@ -4989,7 +4987,7 @@
       <c r="O47" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="P47" s="5">
+      <c r="P47" s="11">
         <v>173458006</v>
       </c>
       <c r="Q47" s="3" t="s">
@@ -4998,7 +4996,7 @@
       <c r="R47" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S47" s="5">
+      <c r="S47" s="11">
         <v>163457006</v>
       </c>
       <c r="T47" s="3" t="s">
@@ -5018,10 +5016,10 @@
       <c r="B48" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48" s="11">
         <v>123456007</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="11">
         <v>173456007</v>
       </c>
       <c r="E48" s="3" t="s">
@@ -5030,13 +5028,13 @@
       <c r="F48" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G48" s="11">
+      <c r="G48" s="8">
         <v>31504</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I48" s="8">
+      <c r="I48" s="5">
         <v>860402100007</v>
       </c>
       <c r="J48" s="3" t="s">
@@ -5048,7 +5046,7 @@
       <c r="L48" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="M48" s="5">
+      <c r="M48" s="11">
         <v>163457007</v>
       </c>
       <c r="N48" s="3" t="s">
@@ -5057,7 +5055,7 @@
       <c r="O48" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="P48" s="5">
+      <c r="P48" s="11">
         <v>173458007</v>
       </c>
       <c r="Q48" s="3" t="s">
@@ -5066,7 +5064,7 @@
       <c r="R48" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="S48" s="5">
+      <c r="S48" s="11">
         <v>173458007</v>
       </c>
       <c r="T48" s="3" t="s">
@@ -5086,10 +5084,10 @@
       <c r="B49" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="C49" s="5">
+      <c r="C49" s="11">
         <v>123456008</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="11">
         <v>173456008</v>
       </c>
       <c r="E49" s="3" t="s">
@@ -5098,13 +5096,13 @@
       <c r="F49" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G49" s="11">
+      <c r="G49" s="8">
         <v>31979</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I49" s="8">
+      <c r="I49" s="5">
         <v>870721100008</v>
       </c>
       <c r="J49" s="3" t="s">
@@ -5116,7 +5114,7 @@
       <c r="L49" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="M49" s="5">
+      <c r="M49" s="11">
         <v>163457008</v>
       </c>
       <c r="N49" s="3" t="s">
@@ -5125,7 +5123,7 @@
       <c r="O49" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="P49" s="5">
+      <c r="P49" s="11">
         <v>173458008</v>
       </c>
       <c r="Q49" s="3" t="s">
@@ -5134,7 +5132,7 @@
       <c r="R49" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="S49" s="5">
+      <c r="S49" s="11">
         <v>173458008</v>
       </c>
       <c r="T49" s="3" t="s">
@@ -5154,10 +5152,10 @@
       <c r="B50" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C50" s="11">
         <v>123456009</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="11">
         <v>173456009</v>
       </c>
       <c r="E50" s="3" t="s">
@@ -5166,13 +5164,13 @@
       <c r="F50" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G50" s="11">
+      <c r="G50" s="8">
         <v>32205</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I50" s="8">
+      <c r="I50" s="5">
         <v>880303100009</v>
       </c>
       <c r="J50" s="3" t="s">
@@ -5184,7 +5182,7 @@
       <c r="L50" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="M50" s="5">
+      <c r="M50" s="11">
         <v>163457009</v>
       </c>
       <c r="N50" s="3" t="s">
@@ -5193,7 +5191,7 @@
       <c r="O50" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="P50" s="5">
+      <c r="P50" s="11">
         <v>173458009</v>
       </c>
       <c r="Q50" s="3" t="s">
@@ -5202,7 +5200,7 @@
       <c r="R50" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S50" s="5">
+      <c r="S50" s="11">
         <v>163457009</v>
       </c>
       <c r="T50" s="3" t="s">
@@ -5222,10 +5220,10 @@
       <c r="B51" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C51" s="11">
         <v>123456010</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51" s="11">
         <v>173456010</v>
       </c>
       <c r="E51" s="3" t="s">
@@ -5234,13 +5232,13 @@
       <c r="F51" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G51" s="11">
+      <c r="G51" s="8">
         <v>32823</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I51" s="8">
+      <c r="I51" s="5">
         <v>891111100010</v>
       </c>
       <c r="J51" s="3" t="s">
@@ -5252,7 +5250,7 @@
       <c r="L51" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="M51" s="5">
+      <c r="M51" s="11">
         <v>163457010</v>
       </c>
       <c r="N51" s="3" t="s">
@@ -5261,7 +5259,7 @@
       <c r="O51" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="P51" s="5">
+      <c r="P51" s="11">
         <v>173458010</v>
       </c>
       <c r="Q51" s="3" t="s">
@@ -5270,7 +5268,7 @@
       <c r="R51" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="S51" s="5">
+      <c r="S51" s="11">
         <v>173458010</v>
       </c>
       <c r="T51" s="3" t="s">
@@ -5290,10 +5288,10 @@
       <c r="B52" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C52" s="11">
         <v>123456011</v>
       </c>
-      <c r="D52" s="5">
+      <c r="D52" s="11">
         <v>173456011</v>
       </c>
       <c r="E52" s="3" t="s">
@@ -5302,13 +5300,13 @@
       <c r="F52" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G52" s="8">
         <v>29266</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I52" s="8">
+      <c r="I52" s="5">
         <v>800215100011</v>
       </c>
       <c r="J52" s="3" t="s">
@@ -5320,7 +5318,7 @@
       <c r="L52" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="M52" s="5">
+      <c r="M52" s="11">
         <v>163457011</v>
       </c>
       <c r="N52" s="3" t="s">
@@ -5329,7 +5327,7 @@
       <c r="O52" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P52" s="5">
+      <c r="P52" s="11">
         <v>173458011</v>
       </c>
       <c r="Q52" s="3" t="s">
@@ -5338,7 +5336,7 @@
       <c r="R52" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S52" s="5">
+      <c r="S52" s="11">
         <v>163457011</v>
       </c>
       <c r="T52" s="3" t="s">
@@ -5358,10 +5356,10 @@
       <c r="B53" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C53" s="5">
+      <c r="C53" s="11">
         <v>123456012</v>
       </c>
-      <c r="D53" s="5">
+      <c r="D53" s="11">
         <v>173456012</v>
       </c>
       <c r="E53" s="3" t="s">
@@ -5370,13 +5368,13 @@
       <c r="F53" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G53" s="11">
+      <c r="G53" s="8">
         <v>29730</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I53" s="8">
+      <c r="I53" s="5">
         <v>810524100012</v>
       </c>
       <c r="J53" s="3" t="s">
@@ -5388,7 +5386,7 @@
       <c r="L53" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="M53" s="5">
+      <c r="M53" s="11">
         <v>163457012</v>
       </c>
       <c r="N53" s="3" t="s">
@@ -5397,7 +5395,7 @@
       <c r="O53" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="P53" s="5">
+      <c r="P53" s="11">
         <v>173458012</v>
       </c>
       <c r="Q53" s="3" t="s">
@@ -5406,7 +5404,7 @@
       <c r="R53" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="S53" s="5">
+      <c r="S53" s="11">
         <v>173458012</v>
       </c>
       <c r="T53" s="3" t="s">
@@ -5426,10 +5424,10 @@
       <c r="B54" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="C54" s="5">
+      <c r="C54" s="11">
         <v>123456013</v>
       </c>
-      <c r="D54" s="5">
+      <c r="D54" s="11">
         <v>173456013</v>
       </c>
       <c r="E54" s="3" t="s">
@@ -5438,13 +5436,13 @@
       <c r="F54" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G54" s="11">
+      <c r="G54" s="8">
         <v>30231</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I54" s="8">
+      <c r="I54" s="5">
         <v>821007100013</v>
       </c>
       <c r="J54" s="3" t="s">
@@ -5456,7 +5454,7 @@
       <c r="L54" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="M54" s="5">
+      <c r="M54" s="11">
         <v>163457013</v>
       </c>
       <c r="N54" s="3" t="s">
@@ -5465,7 +5463,7 @@
       <c r="O54" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="P54" s="5">
+      <c r="P54" s="11">
         <v>173458013</v>
       </c>
       <c r="Q54" s="3" t="s">
@@ -5474,7 +5472,7 @@
       <c r="R54" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S54" s="5">
+      <c r="S54" s="11">
         <v>163457013</v>
       </c>
       <c r="T54" s="3" t="s">
@@ -5494,10 +5492,10 @@
       <c r="B55" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="C55" s="5">
+      <c r="C55" s="11">
         <v>123456014</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D55" s="11">
         <v>173456014</v>
       </c>
       <c r="E55" s="3" t="s">
@@ -5506,13 +5504,13 @@
       <c r="F55" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G55" s="11">
+      <c r="G55" s="8">
         <v>30497</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I55" s="8">
+      <c r="I55" s="5">
         <v>830630100014</v>
       </c>
       <c r="J55" s="3" t="s">
@@ -5524,7 +5522,7 @@
       <c r="L55" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="M55" s="5">
+      <c r="M55" s="11">
         <v>163457014</v>
       </c>
       <c r="N55" s="3" t="s">
@@ -5533,7 +5531,7 @@
       <c r="O55" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="P55" s="5">
+      <c r="P55" s="11">
         <v>173458014</v>
       </c>
       <c r="Q55" s="3" t="s">
@@ -5542,7 +5540,7 @@
       <c r="R55" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="S55" s="5">
+      <c r="S55" s="11">
         <v>173458014</v>
       </c>
       <c r="T55" s="3" t="s">
@@ -5562,10 +5560,10 @@
       <c r="B56" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C56" s="11">
         <v>123456015</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D56" s="11">
         <v>173456015</v>
       </c>
       <c r="E56" s="3" t="s">
@@ -5574,13 +5572,13 @@
       <c r="F56" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G56" s="11">
+      <c r="G56" s="8">
         <v>30693</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I56" s="8">
+      <c r="I56" s="5">
         <v>840112100015</v>
       </c>
       <c r="J56" s="3" t="s">
@@ -5592,7 +5590,7 @@
       <c r="L56" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="M56" s="5">
+      <c r="M56" s="11">
         <v>163457015</v>
       </c>
       <c r="N56" s="3" t="s">
@@ -5601,7 +5599,7 @@
       <c r="O56" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="P56" s="5">
+      <c r="P56" s="11">
         <v>173458015</v>
       </c>
       <c r="Q56" s="3" t="s">
@@ -5610,7 +5608,7 @@
       <c r="R56" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S56" s="5">
+      <c r="S56" s="11">
         <v>163457015</v>
       </c>
       <c r="T56" s="3" t="s">
@@ -5630,10 +5628,10 @@
       <c r="B57" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="C57" s="5">
+      <c r="C57" s="11">
         <v>123456016</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D57" s="11">
         <v>173456016</v>
       </c>
       <c r="E57" s="3" t="s">
@@ -5642,13 +5640,13 @@
       <c r="F57" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G57" s="11">
+      <c r="G57" s="8">
         <v>31126</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I57" s="8">
+      <c r="I57" s="5">
         <v>850320100016</v>
       </c>
       <c r="J57" s="3" t="s">
@@ -5660,7 +5658,7 @@
       <c r="L57" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="M57" s="5">
+      <c r="M57" s="11">
         <v>163457016</v>
       </c>
       <c r="N57" s="3" t="s">
@@ -5669,7 +5667,7 @@
       <c r="O57" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="P57" s="5">
+      <c r="P57" s="11">
         <v>173458016</v>
       </c>
       <c r="Q57" s="3" t="s">
@@ -5678,7 +5676,7 @@
       <c r="R57" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="S57" s="5">
+      <c r="S57" s="11">
         <v>173458016</v>
       </c>
       <c r="T57" s="3" t="s">
@@ -5698,10 +5696,10 @@
       <c r="B58" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C58" s="11">
         <v>123456017</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="11">
         <v>173456017</v>
       </c>
       <c r="E58" s="3" t="s">
@@ -5710,13 +5708,13 @@
       <c r="F58" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G58" s="11">
+      <c r="G58" s="8">
         <v>31598</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I58" s="8">
+      <c r="I58" s="5">
         <v>860705100017</v>
       </c>
       <c r="J58" s="3" t="s">
@@ -5728,7 +5726,7 @@
       <c r="L58" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="M58" s="5">
+      <c r="M58" s="11">
         <v>163457017</v>
       </c>
       <c r="N58" s="3" t="s">
@@ -5737,7 +5735,7 @@
       <c r="O58" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P58" s="5">
+      <c r="P58" s="11">
         <v>173458017</v>
       </c>
       <c r="Q58" s="3" t="s">
@@ -5746,7 +5744,7 @@
       <c r="R58" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S58" s="5">
+      <c r="S58" s="11">
         <v>163457017</v>
       </c>
       <c r="T58" s="3" t="s">
@@ -5766,10 +5764,10 @@
       <c r="B59" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="C59" s="5">
+      <c r="C59" s="11">
         <v>123456018</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D59" s="11">
         <v>173456018</v>
       </c>
       <c r="E59" s="3" t="s">
@@ -5778,13 +5776,13 @@
       <c r="F59" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G59" s="11">
+      <c r="G59" s="8">
         <v>32125</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I59" s="8">
+      <c r="I59" s="5">
         <v>871214100018</v>
       </c>
       <c r="J59" s="3" t="s">
@@ -5796,7 +5794,7 @@
       <c r="L59" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="M59" s="5">
+      <c r="M59" s="11">
         <v>163457018</v>
       </c>
       <c r="N59" s="3" t="s">
@@ -5805,7 +5803,7 @@
       <c r="O59" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="P59" s="5">
+      <c r="P59" s="11">
         <v>173458018</v>
       </c>
       <c r="Q59" s="3" t="s">
@@ -5814,7 +5812,7 @@
       <c r="R59" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="S59" s="5">
+      <c r="S59" s="11">
         <v>173458018</v>
       </c>
       <c r="T59" s="3" t="s">
@@ -5834,10 +5832,10 @@
       <c r="B60" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="C60" s="5">
+      <c r="C60" s="11">
         <v>123456019</v>
       </c>
-      <c r="D60" s="5">
+      <c r="D60" s="11">
         <v>173456019</v>
       </c>
       <c r="E60" s="3" t="s">
@@ -5846,13 +5844,13 @@
       <c r="F60" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G60" s="11">
+      <c r="G60" s="8">
         <v>32469</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I60" s="8">
+      <c r="I60" s="5">
         <v>881122100019</v>
       </c>
       <c r="J60" s="3" t="s">
@@ -5864,7 +5862,7 @@
       <c r="L60" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="M60" s="5">
+      <c r="M60" s="11">
         <v>163457019</v>
       </c>
       <c r="N60" s="3" t="s">
@@ -5873,7 +5871,7 @@
       <c r="O60" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="P60" s="5">
+      <c r="P60" s="11">
         <v>173458019</v>
       </c>
       <c r="Q60" s="3" t="s">
@@ -5882,7 +5880,7 @@
       <c r="R60" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S60" s="5">
+      <c r="S60" s="11">
         <v>163457019</v>
       </c>
       <c r="T60" s="3" t="s">
@@ -5902,10 +5900,10 @@
       <c r="B61" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="C61" s="5">
+      <c r="C61" s="11">
         <v>123456020</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D61" s="11">
         <v>173456020</v>
       </c>
       <c r="E61" s="3" t="s">
@@ -5914,13 +5912,13 @@
       <c r="F61" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G61" s="11">
+      <c r="G61" s="8">
         <v>32606</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I61" s="8">
+      <c r="I61" s="5">
         <v>890408100020</v>
       </c>
       <c r="J61" s="3" t="s">
@@ -5932,7 +5930,7 @@
       <c r="L61" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="M61" s="5">
+      <c r="M61" s="11">
         <v>163457020</v>
       </c>
       <c r="N61" s="3" t="s">
@@ -5941,7 +5939,7 @@
       <c r="O61" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="P61" s="5">
+      <c r="P61" s="11">
         <v>173458020</v>
       </c>
       <c r="Q61" s="3" t="s">
@@ -5950,7 +5948,7 @@
       <c r="R61" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="S61" s="5">
+      <c r="S61" s="11">
         <v>173458020</v>
       </c>
       <c r="T61" s="3" t="s">
@@ -5970,10 +5968,10 @@
       <c r="B62" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C62" s="5">
+      <c r="C62" s="11">
         <v>123456021</v>
       </c>
-      <c r="D62" s="5">
+      <c r="D62" s="11">
         <v>173456021</v>
       </c>
       <c r="E62" s="3" t="s">
@@ -5982,13 +5980,13 @@
       <c r="F62" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G62" s="11">
+      <c r="G62" s="8">
         <v>32905</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="8">
+      <c r="I62" s="5">
         <v>900201100021</v>
       </c>
       <c r="J62" s="3" t="s">
@@ -6000,7 +5998,7 @@
       <c r="L62" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="M62" s="5">
+      <c r="M62" s="11">
         <v>163457021</v>
       </c>
       <c r="N62" s="3" t="s">
@@ -6009,7 +6007,7 @@
       <c r="O62" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="P62" s="5">
+      <c r="P62" s="11">
         <v>173458021</v>
       </c>
       <c r="Q62" s="3" t="s">
@@ -6018,7 +6016,7 @@
       <c r="R62" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S62" s="5">
+      <c r="S62" s="11">
         <v>163457021</v>
       </c>
       <c r="T62" s="3" t="s">
@@ -6038,10 +6036,10 @@
       <c r="B63" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="C63" s="5">
+      <c r="C63" s="11">
         <v>123456022</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D63" s="11">
         <v>173456022</v>
       </c>
       <c r="E63" s="3" t="s">
@@ -6050,13 +6048,13 @@
       <c r="F63" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G63" s="11">
+      <c r="G63" s="8">
         <v>29663</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I63" s="8">
+      <c r="I63" s="5">
         <v>810318100022</v>
       </c>
       <c r="J63" s="3" t="s">
@@ -6068,7 +6066,7 @@
       <c r="L63" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="M63" s="5">
+      <c r="M63" s="11">
         <v>163457022</v>
       </c>
       <c r="N63" s="3" t="s">
@@ -6077,7 +6075,7 @@
       <c r="O63" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="P63" s="5">
+      <c r="P63" s="11">
         <v>173458022</v>
       </c>
       <c r="Q63" s="3" t="s">
@@ -6086,7 +6084,7 @@
       <c r="R63" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S63" s="5">
+      <c r="S63" s="11">
         <v>163457022</v>
       </c>
       <c r="T63" s="3" t="s">
@@ -6106,10 +6104,10 @@
       <c r="B64" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="C64" s="5">
+      <c r="C64" s="11">
         <v>123456023</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D64" s="11">
         <v>173456023</v>
       </c>
       <c r="E64" s="3" t="s">
@@ -6118,13 +6116,13 @@
       <c r="F64" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G64" s="11">
+      <c r="G64" s="8">
         <v>30131</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I64" s="8">
+      <c r="I64" s="5">
         <v>820629100023</v>
       </c>
       <c r="J64" s="3" t="s">
@@ -6136,7 +6134,7 @@
       <c r="L64" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="M64" s="5">
+      <c r="M64" s="11">
         <v>163457023</v>
       </c>
       <c r="N64" s="3" t="s">
@@ -6145,7 +6143,7 @@
       <c r="O64" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="P64" s="5">
+      <c r="P64" s="11">
         <v>173458023</v>
       </c>
       <c r="Q64" s="3" t="s">
@@ -6154,7 +6152,7 @@
       <c r="R64" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S64" s="5">
+      <c r="S64" s="11">
         <v>163457023</v>
       </c>
       <c r="T64" s="3" t="s">
@@ -6174,10 +6172,10 @@
       <c r="B65" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="C65" s="5">
+      <c r="C65" s="11">
         <v>123456024</v>
       </c>
-      <c r="D65" s="5">
+      <c r="D65" s="11">
         <v>173456024</v>
       </c>
       <c r="E65" s="3" t="s">
@@ -6186,13 +6184,13 @@
       <c r="F65" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G65" s="11">
+      <c r="G65" s="8">
         <v>30531</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I65" s="8">
+      <c r="I65" s="5">
         <v>830803100024</v>
       </c>
       <c r="J65" s="3" t="s">
@@ -6204,7 +6202,7 @@
       <c r="L65" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="M65" s="5">
+      <c r="M65" s="11">
         <v>163457024</v>
       </c>
       <c r="N65" s="3" t="s">
@@ -6213,7 +6211,7 @@
       <c r="O65" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="P65" s="5">
+      <c r="P65" s="11">
         <v>173458024</v>
       </c>
       <c r="Q65" s="3" t="s">
@@ -6222,7 +6220,7 @@
       <c r="R65" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="S65" s="5">
+      <c r="S65" s="11">
         <v>173458024</v>
       </c>
       <c r="T65" s="3" t="s">
@@ -6242,10 +6240,10 @@
       <c r="B66" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="C66" s="5">
+      <c r="C66" s="11">
         <v>123456025</v>
       </c>
-      <c r="D66" s="5">
+      <c r="D66" s="11">
         <v>173456025</v>
       </c>
       <c r="E66" s="3" t="s">
@@ -6254,13 +6252,13 @@
       <c r="F66" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G66" s="11">
+      <c r="G66" s="8">
         <v>30998</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I66" s="8">
+      <c r="I66" s="5">
         <v>841112100025</v>
       </c>
       <c r="J66" s="3" t="s">
@@ -6272,7 +6270,7 @@
       <c r="L66" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="M66" s="5">
+      <c r="M66" s="11">
         <v>163457025</v>
       </c>
       <c r="N66" s="3" t="s">
@@ -6281,7 +6279,7 @@
       <c r="O66" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="P66" s="5">
+      <c r="P66" s="11">
         <v>173458025</v>
       </c>
       <c r="Q66" s="3" t="s">
@@ -6290,7 +6288,7 @@
       <c r="R66" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S66" s="5">
+      <c r="S66" s="11">
         <v>163457025</v>
       </c>
       <c r="T66" s="3" t="s">
@@ -6310,10 +6308,10 @@
       <c r="B67" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="C67" s="5">
+      <c r="C67" s="11">
         <v>123456026</v>
       </c>
-      <c r="D67" s="5">
+      <c r="D67" s="11">
         <v>173456026</v>
       </c>
       <c r="E67" s="3" t="s">
@@ -6322,13 +6320,13 @@
       <c r="F67" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G67" s="11">
+      <c r="G67" s="8">
         <v>31317</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I67" s="8">
+      <c r="I67" s="5">
         <v>850927100026</v>
       </c>
       <c r="J67" s="3" t="s">
@@ -6340,7 +6338,7 @@
       <c r="L67" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="M67" s="5">
+      <c r="M67" s="11">
         <v>163457026</v>
       </c>
       <c r="N67" s="3" t="s">
@@ -6349,7 +6347,7 @@
       <c r="O67" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="P67" s="5">
+      <c r="P67" s="11">
         <v>173458026</v>
       </c>
       <c r="Q67" s="3" t="s">
@@ -6358,7 +6356,7 @@
       <c r="R67" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="S67" s="5">
+      <c r="S67" s="11">
         <v>173458026</v>
       </c>
       <c r="T67" s="3" t="s">
@@ -6378,10 +6376,10 @@
       <c r="B68" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C68" s="5">
+      <c r="C68" s="11">
         <v>123456027</v>
       </c>
-      <c r="D68" s="5">
+      <c r="D68" s="11">
         <v>173456027</v>
       </c>
       <c r="E68" s="3" t="s">
@@ -6390,13 +6388,13 @@
       <c r="F68" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G68" s="11">
+      <c r="G68" s="8">
         <v>31547</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I68" s="8">
+      <c r="I68" s="5">
         <v>860515100027</v>
       </c>
       <c r="J68" s="3" t="s">
@@ -6408,7 +6406,7 @@
       <c r="L68" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="M68" s="5">
+      <c r="M68" s="11">
         <v>163457027</v>
       </c>
       <c r="N68" s="3" t="s">
@@ -6417,7 +6415,7 @@
       <c r="O68" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="P68" s="5">
+      <c r="P68" s="11">
         <v>173458027</v>
       </c>
       <c r="Q68" s="3" t="s">
@@ -6426,7 +6424,7 @@
       <c r="R68" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S68" s="5">
+      <c r="S68" s="11">
         <v>163457027</v>
       </c>
       <c r="T68" s="3" t="s">
@@ -6446,10 +6444,10 @@
       <c r="B69" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="C69" s="5">
+      <c r="C69" s="11">
         <v>123456028</v>
       </c>
-      <c r="D69" s="5">
+      <c r="D69" s="11">
         <v>173456028</v>
       </c>
       <c r="E69" s="3" t="s">
@@ -6458,13 +6456,13 @@
       <c r="F69" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G69" s="11">
+      <c r="G69" s="8">
         <v>31816</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I69" s="8">
+      <c r="I69" s="5">
         <v>870208100028</v>
       </c>
       <c r="J69" s="3" t="s">
@@ -6476,7 +6474,7 @@
       <c r="L69" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="M69" s="5">
+      <c r="M69" s="11">
         <v>163457028</v>
       </c>
       <c r="N69" s="3" t="s">
@@ -6485,7 +6483,7 @@
       <c r="O69" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="P69" s="5">
+      <c r="P69" s="11">
         <v>173458028</v>
       </c>
       <c r="Q69" s="3" t="s">
@@ -6494,7 +6492,7 @@
       <c r="R69" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="S69" s="5">
+      <c r="S69" s="11">
         <v>173458028</v>
       </c>
       <c r="T69" s="3" t="s">
@@ -6514,10 +6512,10 @@
       <c r="B70" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="C70" s="5">
+      <c r="C70" s="11">
         <v>123456029</v>
       </c>
-      <c r="D70" s="5">
+      <c r="D70" s="11">
         <v>173456029</v>
       </c>
       <c r="E70" s="3" t="s">
@@ -6526,13 +6524,13 @@
       <c r="F70" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G70" s="11">
+      <c r="G70" s="8">
         <v>32344</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I70" s="8">
+      <c r="I70" s="5">
         <v>880720100029</v>
       </c>
       <c r="J70" s="3" t="s">
@@ -6544,7 +6542,7 @@
       <c r="L70" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="M70" s="5">
+      <c r="M70" s="11">
         <v>163457029</v>
       </c>
       <c r="N70" s="3" t="s">
@@ -6553,7 +6551,7 @@
       <c r="O70" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="P70" s="5">
+      <c r="P70" s="11">
         <v>173458029</v>
       </c>
       <c r="Q70" s="3" t="s">
@@ -6562,7 +6560,7 @@
       <c r="R70" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="S70" s="5">
+      <c r="S70" s="11">
         <v>163457029</v>
       </c>
       <c r="T70" s="3" t="s">
@@ -6582,11 +6580,11 @@
       <c r="B71" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="11">
+        <v>123456030</v>
+      </c>
+      <c r="D71" s="11" t="s">
         <v>426</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>427</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>2</v>
@@ -6594,47 +6592,47 @@
       <c r="F71" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G71" s="11">
+      <c r="G71" s="8">
         <v>33156</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I71" s="8">
+      <c r="I71" s="5">
         <v>901010992346</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K71" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="L71" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="L71" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="M71" s="5" t="s">
-        <v>427</v>
+      <c r="M71" s="11">
+        <v>163457030</v>
       </c>
       <c r="N71" s="3" t="s">
         <v>299</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="P71" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
+      </c>
+      <c r="P71" s="11">
+        <v>173458030</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>19</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="S71" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
+      </c>
+      <c r="S71" s="11" t="s">
+        <v>430</v>
       </c>
       <c r="T71" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="U71" s="3" t="s">
         <v>82</v>
@@ -6651,5 +6649,6 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>